--- a/ATP_Player_Scouting top150.xlsx
+++ b/ATP_Player_Scouting top150.xlsx
@@ -119,9 +119,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,21 +488,21 @@
   <dimension ref="A1:L159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" style="11" min="1" max="1"/>
+    <col width="26" customWidth="1" style="11" min="2" max="2"/>
+    <col width="9" customWidth="1" style="11" min="3" max="3"/>
+    <col width="16" customWidth="1" style="11" min="4" max="4"/>
+    <col width="34" customWidth="1" style="11" min="5" max="5"/>
+    <col width="30" customWidth="1" style="11" min="6" max="6"/>
+    <col width="46" customWidth="1" style="11" min="7" max="7"/>
+    <col width="46" customWidth="1" style="11" min="8" max="8"/>
+    <col width="42" customWidth="1" style="11" min="9" max="9"/>
+    <col width="42" customWidth="1" style="11" min="10" max="10"/>
+    <col width="70" customWidth="1" style="11" min="11" max="11"/>
+    <col width="14" customWidth="1" style="11" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="11">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
@@ -2457,12 +2455,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Consistency; movement; solid backhand; steady temperament</t>
+          <t>Consistency; movement; solid backhand; steady temperament; serve solid — 67.2% serve pts won, top quartile 2026 (measured 17.08.2026)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Lacks a big put-away weapon; serve only modest</t>
+          <t>Lacks a big put-away weapon; return below field average (39.1% vs 41.2% median, measured 17.08.2026)</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4377,12 +4375,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Heavy forehand; big serve for size; clean 2H BH; good return + defense (Miami+Rome QFs 2026)</t>
+          <t>Heavy forehand; clean 2H BH; good return + defense (Miami+Rome QFs 2026)</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Young consistency; still building the ceiling</t>
+          <t>Young consistency; still building the ceiling; serve not yet a weapon — 61.9% serve pts won, bottom quartile 2026 (measured 17.08.2026)</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -5807,7 +5805,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Aggressive baseliner (big serve)</t>
+          <t>Aggressive baseliner (fast serve, not a dominant one)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -5817,7 +5815,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Big serve (&gt;200 km/h); power off both wings; clay; return/break</t>
+          <t>Serve is fast (&gt;200 km/h) but NOT dominant — 61.3% serve pts won and 57.9% 1st serves in, both bottom quartile 2026 (measured 17.08.2026); power off both wings; clay; return/break 42.5%, above field median</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -9574,42 +9572,42 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="11" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Confidence: High &gt; Med-High &gt; Med &gt; Med-Low &gt; Low &gt; Insufficient. Model koristi profil SAMO od Med-Low navise; Low i Insufficient se ignoriraju.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Profil utjece na procjenu najvise +/-3pp i sluzi kao tie-breaker kad su mjereni faktori izjednaceni — nikada ne moze nadjacati ELO, formu ili statistiku servisa.</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>Profili rangova ~100-150 (dodani 31.07.2026) IZVEDENI su iz mjerenih podataka (3-godisnji ucinak po podlogama, hold%, return points won, ace rate, surface ELO), a ne iz neovisnog skautiranja. Gdje podatka nema, pise 'cannot be determined'.</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="11" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>Za igrace ranga &gt;100 trogodisnji W-L ukljucuje i Challenger/ITF razinu, pa je stvarna kvaliteta na ATP razini obicno niza od sirovog postotka.</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="11" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>Ako se vanjski opis i izmjerene brojke ne slazu, u biljesci stoji CONFLICT i uputa da se vjeruje izmjerenom (primjer: Arthur Gea).</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="11" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>Uredjivanje: promijeni sto zelis pa pokreni  python scripts/import_scouting.py  da se vrati u Supabase. Supabase je izvor istine za dnevni model.</t>
         </is>

--- a/ATP_Player_Scouting top150.xlsx
+++ b/ATP_Player_Scouting top150.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L159"/>
+  <dimension ref="A1:FU159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="11" min="1" max="1"/>
@@ -563,6 +563,21 @@
           <t>Confidence / Pouzdanost</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Height (cm)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Plays / Igra</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -683,6 +698,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -803,6 +833,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -863,6 +908,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -923,6 +983,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1043,6 +1118,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1103,6 +1193,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1163,6 +1268,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1283,6 +1403,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1343,6 +1478,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1403,6 +1553,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1463,6 +1628,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1523,6 +1703,21 @@
           <t>Insufficient</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1583,6 +1778,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1643,6 +1853,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1703,6 +1928,21 @@
           <t>Insufficient</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1823,6 +2063,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1883,6 +2138,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1943,6 +2213,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2003,6 +2288,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2063,6 +2363,21 @@
           <t>Insufficient</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2123,6 +2438,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2183,6 +2513,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2243,6 +2588,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2303,6 +2663,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2363,6 +2738,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2423,6 +2813,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2483,6 +2888,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2543,6 +2963,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2603,6 +3038,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2663,6 +3113,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2723,6 +3188,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2783,6 +3263,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2843,6 +3338,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2903,6 +3413,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3023,6 +3548,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3083,6 +3623,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3143,6 +3698,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3203,6 +3773,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3323,6 +3908,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3383,6 +3983,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3443,6 +4058,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3503,6 +4133,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3563,6 +4208,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3623,6 +4283,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3683,6 +4358,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3743,6 +4433,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3803,6 +4508,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3863,6 +4583,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3923,6 +4658,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3983,6 +4733,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4043,6 +4808,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -4103,6 +4883,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -4163,6 +4958,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -4223,6 +5033,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -4283,6 +5108,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4343,6 +5183,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4403,6 +5258,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4463,6 +5333,21 @@
           <t>Insufficient</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -4583,6 +5468,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -4643,6 +5543,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4703,6 +5618,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Left-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4763,6 +5693,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4823,6 +5768,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4883,6 +5843,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -5003,6 +5978,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -5063,6 +6053,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -5123,6 +6128,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -5183,6 +6203,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -5243,6 +6278,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -5303,6 +6353,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -5363,6 +6428,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -5543,6 +6623,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -5723,6 +6818,21 @@
           <t>Med-High</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5843,6 +6953,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Right-Handed, Unknown Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5963,6 +7088,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -6023,6 +7163,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -6083,6 +7238,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -6203,6 +7373,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -6323,6 +7508,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6383,6 +7583,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -6443,6 +7658,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6503,6 +7733,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -6563,6 +7808,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6683,6 +7943,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6743,6 +8018,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -6803,6 +8093,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -6863,6 +8168,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -6923,6 +8243,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6983,6 +8318,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -7043,6 +8393,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -7103,6 +8468,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -7163,6 +8543,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -7223,6 +8618,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -7283,6 +8693,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -7343,6 +8768,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -7403,6 +8843,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -7463,6 +8918,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7523,6 +8993,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -7583,6 +9068,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -7643,6 +9143,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7703,6 +9218,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7763,6 +9293,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7823,6 +9368,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -7883,6 +9443,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7943,6 +9518,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -8003,6 +9593,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -8063,6 +9668,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -8123,6 +9743,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -8183,6 +9818,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -8243,6 +9893,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -8303,6 +9968,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -8363,6 +10043,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -8423,6 +10118,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -8483,6 +10193,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -8543,6 +10268,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -8603,6 +10343,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -8663,6 +10418,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -8723,6 +10493,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -8783,6 +10568,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -8843,6 +10643,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -8903,6 +10718,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -8963,6 +10793,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Right-Handed, One-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -9023,6 +10868,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -9083,6 +10943,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -9143,6 +11018,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -9203,6 +11093,21 @@
           <t>Med</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -9263,6 +11168,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -9323,6 +11243,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -9383,6 +11318,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Left-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -9443,6 +11393,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -9503,6 +11468,21 @@
           <t>Med-Low</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -9563,7 +11543,23 @@
           <t>Med-Low</t>
         </is>
       </c>
-    </row>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Right-Handed, Two-Handed Backhand</t>
+        </is>
+      </c>
+    </row>
+    <row r="152"/>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
